--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260806.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260806.xlsx
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>580,000</t>
+          <t>1,010,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>580,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>1,250,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,250,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
